--- a/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
+++ b/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:39:33+00:00</t>
+    <t>2026-09-23T11:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
+++ b/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:46:09+00:00</t>
+    <t>2026-09-23T12:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
+++ b/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:15:24+00:00</t>
+    <t>2026-09-23T12:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
+++ b/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:19:55+00:00</t>
+    <t>2026-09-23T12:32:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
+++ b/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="133">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:32:00+00:00</t>
+    <t>2026-09-23T18:28:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -407,13 +407,6 @@
   </si>
   <si>
     <t>Hash algorithm (hash only), e.g. 'hmac-sha256'.</t>
-  </si>
-  <si>
-    <t>deidentification-ruleset.rule.propagateTo</t>
-  </si>
-  <si>
-    <t>Reference paths rewritten with the same hash (hash on an id element),
-     e.g. '*.subject', '*.patient'.</t>
   </si>
   <si>
     <t>deidentification-ruleset.rule.maxDays</t>
@@ -741,7 +734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.4453125" customWidth="true" bestFit="true"/>
@@ -2111,7 +2104,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2123,7 +2116,7 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>126</v>
@@ -2186,7 +2179,7 @@
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2423,7 +2416,7 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>132</v>
@@ -2492,106 +2485,6 @@
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
+++ b/feature-th-deidentification/StructureDefinition-deidentification-ruleset.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://ig.santeon.nl/careplan/StructureDefinition/deidentification-ruleset</t>
+    <t>https://ig.santeon.nl/sim-on-fhir/StructureDefinition/deidentification-ruleset</t>
   </si>
   <si>
     <t>Version</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>De-identification Ruleset</t>
+    <t>De-identification ruleset (model)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T18:28:14+00:00</t>
+    <t>2026-10-16T14:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -389,7 +389,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://ig.santeon.nl/careplan/ValueSet/deidentification-action-vs</t>
+    <t>https://ig.santeon.nl/sim-on-fhir/ValueSet/deidentification-action-vs</t>
   </si>
   <si>
     <t>deidentification-ruleset.rule.priority</t>
@@ -762,7 +762,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.12109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
